--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.413583274822</v>
+        <v>8.192207282158575</v>
       </c>
       <c r="D2" t="n">
-        <v>28.22909406222588</v>
+        <v>4.587227785111706</v>
       </c>
       <c r="E2" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F2" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.2462484236173</v>
+        <v>5.565015368837812</v>
       </c>
       <c r="D3" t="n">
-        <v>34.17472761724557</v>
+        <v>5.553393237802406</v>
       </c>
       <c r="E3" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F3" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.70663399276923</v>
+        <v>10.189828023825</v>
       </c>
       <c r="D4" t="n">
-        <v>53.11422247039877</v>
+        <v>8.6310611514398</v>
       </c>
       <c r="E4" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F4" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.26827326933983</v>
+        <v>7.518594406267723</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20456047368845</v>
+        <v>6.045741076974372</v>
       </c>
       <c r="E5" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F5" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.60267398352586</v>
+        <v>5.622934522322953</v>
       </c>
       <c r="D6" t="n">
-        <v>18.83282302289105</v>
+        <v>3.060333741219795</v>
       </c>
       <c r="E6" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F6" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.64209251698571</v>
+        <v>6.279340034010178</v>
       </c>
       <c r="D7" t="n">
-        <v>12.72291826788706</v>
+        <v>2.067474218531647</v>
       </c>
       <c r="E7" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F7" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.15788909823142</v>
+        <v>10.58815697846261</v>
       </c>
       <c r="D8" t="n">
-        <v>51.53705304780146</v>
+        <v>8.374771120267738</v>
       </c>
       <c r="E8" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F8" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.89167607735638</v>
+        <v>5.507397362570412</v>
       </c>
       <c r="D9" t="n">
-        <v>20.16291041501638</v>
+        <v>3.276472942440162</v>
       </c>
       <c r="E9" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F9" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.31426944223578</v>
+        <v>8.988568784363315</v>
       </c>
       <c r="D10" t="n">
-        <v>41.64499240167104</v>
+        <v>6.767311265271545</v>
       </c>
       <c r="E10" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F10" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.157559242836</v>
+        <v>6.363103376960851</v>
       </c>
       <c r="D11" t="n">
-        <v>42.81792198411632</v>
+        <v>6.957912322418902</v>
       </c>
       <c r="E11" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F11" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.41832411221493</v>
+        <v>8.680477668234925</v>
       </c>
       <c r="D12" t="n">
-        <v>34.30014577228499</v>
+        <v>5.573773687996312</v>
       </c>
       <c r="E12" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F12" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.88541757447628</v>
+        <v>10.38138035585239</v>
       </c>
       <c r="D13" t="n">
-        <v>37.96709376802659</v>
+        <v>6.169652737304321</v>
       </c>
       <c r="E13" t="n">
-        <v>11.50333879148261</v>
+        <v>1.869292553615924</v>
       </c>
       <c r="F13" t="n">
-        <v>12.04474105274848</v>
+        <v>1.957270421071629</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
